--- a/artfynd/A 18646-2024 artfynd.xlsx
+++ b/artfynd/A 18646-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,6 +799,1949 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>120189881</v>
+      </c>
+      <c r="B3" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lillträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>781473</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7297275</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120189876</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57421</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lillträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>781433</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7297263</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2st</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120189894</v>
+      </c>
+      <c r="B5" t="n">
+        <v>95202</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lillträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>781369</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7297222</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120189890</v>
+      </c>
+      <c r="B6" t="n">
+        <v>82305</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lillträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>781400</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7297231</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120189870</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79144</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lillträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>781383</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7297243</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120189892</v>
+      </c>
+      <c r="B8" t="n">
+        <v>82305</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lillträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>781383</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7297238</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120189893</v>
+      </c>
+      <c r="B9" t="n">
+        <v>82305</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lillträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>781372</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7297233</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120189879</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78608</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>864</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lillträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>781437</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7297264</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120189888</v>
+      </c>
+      <c r="B11" t="n">
+        <v>82305</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lillträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>781400</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7297236</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120189887</v>
+      </c>
+      <c r="B12" t="n">
+        <v>82305</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lillträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>781443</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7297265</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120189873</v>
+      </c>
+      <c r="B13" t="n">
+        <v>90067</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lillträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>781452</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7297230</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120189885</v>
+      </c>
+      <c r="B14" t="n">
+        <v>82305</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lillträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>781548</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7297260</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120189875</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lillträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>781434</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7297219</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120189878</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78608</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>864</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lillträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>781474</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7297278</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120189872</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90582</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lillträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>781492</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7297280</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120189882</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lillträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>781496</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7297260</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120189869</v>
+      </c>
+      <c r="B19" t="n">
+        <v>90527</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lillträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>781495</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7297296</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120189883</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lillträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>781413</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7297244</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120189877</v>
+      </c>
+      <c r="B21" t="n">
+        <v>93935</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2387</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Källpraktmossa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Pseudobryum cinclidioides</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Huebener) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lillträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>781409</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7297244</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18646-2024 artfynd.xlsx
+++ b/artfynd/A 18646-2024 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120189876</v>
+        <v>120189869</v>
       </c>
       <c r="B4" t="n">
-        <v>57421</v>
+        <v>90527</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +919,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>781433</v>
+        <v>781495</v>
       </c>
       <c r="R4" t="n">
-        <v>7297263</v>
+        <v>7297296</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,11 +979,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2st</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120189894</v>
+        <v>120189872</v>
       </c>
       <c r="B5" t="n">
-        <v>95202</v>
+        <v>90582</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,25 +1017,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1050,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781369</v>
+        <v>781492</v>
       </c>
       <c r="R5" t="n">
-        <v>7297222</v>
+        <v>7297280</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,7 +1107,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120189890</v>
+        <v>120189887</v>
       </c>
       <c r="B6" t="n">
         <v>82305</v>
@@ -1152,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>781400</v>
+        <v>781443</v>
       </c>
       <c r="R6" t="n">
-        <v>7297231</v>
+        <v>7297265</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120189870</v>
+        <v>120189882</v>
       </c>
       <c r="B7" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,21 +1225,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1254,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>781383</v>
+        <v>781496</v>
       </c>
       <c r="R7" t="n">
-        <v>7297243</v>
+        <v>7297260</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120189892</v>
+        <v>120189873</v>
       </c>
       <c r="B8" t="n">
-        <v>82305</v>
+        <v>90067</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>256703</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>781383</v>
+        <v>781452</v>
       </c>
       <c r="R8" t="n">
-        <v>7297238</v>
+        <v>7297230</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,10 +1413,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120189893</v>
+        <v>120189879</v>
       </c>
       <c r="B9" t="n">
-        <v>82305</v>
+        <v>78608</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,21 +1429,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1458,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>781372</v>
+        <v>781437</v>
       </c>
       <c r="R9" t="n">
-        <v>7297233</v>
+        <v>7297264</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1520,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120189879</v>
+        <v>120189883</v>
       </c>
       <c r="B10" t="n">
-        <v>78608</v>
+        <v>78526</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,21 +1531,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1560,10 +1555,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>781437</v>
+        <v>781413</v>
       </c>
       <c r="R10" t="n">
-        <v>7297264</v>
+        <v>7297244</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,7 +1617,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120189888</v>
+        <v>120189893</v>
       </c>
       <c r="B11" t="n">
         <v>82305</v>
@@ -1662,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>781400</v>
+        <v>781372</v>
       </c>
       <c r="R11" t="n">
-        <v>7297236</v>
+        <v>7297233</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120189887</v>
+        <v>120189875</v>
       </c>
       <c r="B12" t="n">
-        <v>82305</v>
+        <v>57326</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1740,21 +1735,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1764,10 +1759,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>781443</v>
+        <v>781434</v>
       </c>
       <c r="R12" t="n">
-        <v>7297265</v>
+        <v>7297219</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1826,10 +1821,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120189873</v>
+        <v>120189876</v>
       </c>
       <c r="B13" t="n">
-        <v>90067</v>
+        <v>57421</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1842,21 +1837,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>256703</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1866,10 +1861,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>781452</v>
+        <v>781433</v>
       </c>
       <c r="R13" t="n">
-        <v>7297230</v>
+        <v>7297263</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1902,6 +1897,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1928,7 +1928,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120189885</v>
+        <v>120189888</v>
       </c>
       <c r="B14" t="n">
         <v>82305</v>
@@ -1968,10 +1968,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>781548</v>
+        <v>781400</v>
       </c>
       <c r="R14" t="n">
-        <v>7297260</v>
+        <v>7297236</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2030,10 +2030,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120189875</v>
+        <v>120189870</v>
       </c>
       <c r="B15" t="n">
-        <v>57326</v>
+        <v>79144</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2046,21 +2046,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>781434</v>
+        <v>781383</v>
       </c>
       <c r="R15" t="n">
-        <v>7297219</v>
+        <v>7297243</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2132,10 +2132,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120189878</v>
+        <v>120189890</v>
       </c>
       <c r="B16" t="n">
-        <v>78608</v>
+        <v>82305</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2148,21 +2148,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>781474</v>
+        <v>781400</v>
       </c>
       <c r="R16" t="n">
-        <v>7297278</v>
+        <v>7297231</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2234,10 +2234,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120189872</v>
+        <v>120189877</v>
       </c>
       <c r="B17" t="n">
-        <v>90582</v>
+        <v>93935</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2246,25 +2246,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>2387</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2274,10 +2274,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>781492</v>
+        <v>781409</v>
       </c>
       <c r="R17" t="n">
-        <v>7297280</v>
+        <v>7297244</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,10 +2336,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120189882</v>
+        <v>120189892</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2352,21 +2352,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>781496</v>
+        <v>781383</v>
       </c>
       <c r="R18" t="n">
-        <v>7297260</v>
+        <v>7297238</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120189869</v>
+        <v>120189885</v>
       </c>
       <c r="B19" t="n">
-        <v>90527</v>
+        <v>82305</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2450,25 +2450,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2478,10 +2478,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>781495</v>
+        <v>781548</v>
       </c>
       <c r="R19" t="n">
-        <v>7297296</v>
+        <v>7297260</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2540,10 +2540,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120189883</v>
+        <v>120189878</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
+        <v>78608</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2556,21 +2556,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>781413</v>
+        <v>781474</v>
       </c>
       <c r="R20" t="n">
-        <v>7297244</v>
+        <v>7297278</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2642,10 +2642,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120189877</v>
+        <v>120189894</v>
       </c>
       <c r="B21" t="n">
-        <v>93935</v>
+        <v>95202</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2658,21 +2658,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2387</v>
+        <v>2869</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>781409</v>
+        <v>781369</v>
       </c>
       <c r="R21" t="n">
-        <v>7297244</v>
+        <v>7297222</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 18646-2024 artfynd.xlsx
+++ b/artfynd/A 18646-2024 artfynd.xlsx
@@ -1413,10 +1413,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120189879</v>
+        <v>120189883</v>
       </c>
       <c r="B9" t="n">
-        <v>78608</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,21 +1429,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>781437</v>
+        <v>781413</v>
       </c>
       <c r="R9" t="n">
-        <v>7297264</v>
+        <v>7297244</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120189883</v>
+        <v>120189879</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
+        <v>78608</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,21 +1531,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>781413</v>
+        <v>781437</v>
       </c>
       <c r="R10" t="n">
-        <v>7297244</v>
+        <v>7297264</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 18646-2024 artfynd.xlsx
+++ b/artfynd/A 18646-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1413,10 +1413,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120189883</v>
+        <v>120189879</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>78608</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,21 +1429,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>781413</v>
+        <v>781437</v>
       </c>
       <c r="R9" t="n">
-        <v>7297244</v>
+        <v>7297264</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120189879</v>
+        <v>120189883</v>
       </c>
       <c r="B10" t="n">
-        <v>78608</v>
+        <v>78526</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,21 +1531,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>781437</v>
+        <v>781413</v>
       </c>
       <c r="R10" t="n">
-        <v>7297264</v>
+        <v>7297244</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2742,6 +2742,732 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120275854</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78608</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>864</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lillträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>781526</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7297306</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120275859</v>
+      </c>
+      <c r="B23" t="n">
+        <v>74630</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>308</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lillträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>781452</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7297246</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120275858</v>
+      </c>
+      <c r="B24" t="n">
+        <v>82305</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lillträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>781524</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7297322</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120275853</v>
+      </c>
+      <c r="B25" t="n">
+        <v>90724</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1588</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Violmussling</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Trichaptum laricinum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lillträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>781466</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7297264</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120275855</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78608</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>864</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lillträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>781492</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7297238</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120275857</v>
+      </c>
+      <c r="B27" t="n">
+        <v>56514</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lillträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>781512</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7297310</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120275860</v>
+      </c>
+      <c r="B28" t="n">
+        <v>77910</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lillträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>781459</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7297274</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18646-2024 artfynd.xlsx
+++ b/artfynd/A 18646-2024 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120189881</v>
+        <v>120189882</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>781473</v>
+        <v>781496</v>
       </c>
       <c r="R3" t="n">
-        <v>7297275</v>
+        <v>7297260</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120189869</v>
+        <v>120189881</v>
       </c>
       <c r="B4" t="n">
-        <v>90527</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,25 +915,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>781495</v>
+        <v>781473</v>
       </c>
       <c r="R4" t="n">
-        <v>7297296</v>
+        <v>7297275</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120189872</v>
+        <v>120189885</v>
       </c>
       <c r="B5" t="n">
-        <v>90582</v>
+        <v>82321</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,21 +1021,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781492</v>
+        <v>781548</v>
       </c>
       <c r="R5" t="n">
-        <v>7297280</v>
+        <v>7297260</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1110,7 @@
         <v>120189887</v>
       </c>
       <c r="B6" t="n">
-        <v>82305</v>
+        <v>82321</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120189882</v>
+        <v>120189879</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
+        <v>78624</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,21 +1225,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>781496</v>
+        <v>781437</v>
       </c>
       <c r="R7" t="n">
-        <v>7297260</v>
+        <v>7297264</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120189873</v>
+        <v>120189890</v>
       </c>
       <c r="B8" t="n">
-        <v>90067</v>
+        <v>82321</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>256703</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>781452</v>
+        <v>781400</v>
       </c>
       <c r="R8" t="n">
-        <v>7297230</v>
+        <v>7297231</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,10 +1413,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120189883</v>
+        <v>120189893</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>82321</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,21 +1429,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>781413</v>
+        <v>781372</v>
       </c>
       <c r="R9" t="n">
-        <v>7297244</v>
+        <v>7297233</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120189879</v>
+        <v>120189872</v>
       </c>
       <c r="B10" t="n">
-        <v>78608</v>
+        <v>90600</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,21 +1531,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>864</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>781437</v>
+        <v>781492</v>
       </c>
       <c r="R10" t="n">
-        <v>7297264</v>
+        <v>7297280</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,10 +1617,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120189893</v>
+        <v>120189876</v>
       </c>
       <c r="B11" t="n">
-        <v>82305</v>
+        <v>57431</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,25 +1629,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>103031</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>781372</v>
+        <v>781433</v>
       </c>
       <c r="R11" t="n">
-        <v>7297233</v>
+        <v>7297263</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,6 +1693,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1719,10 +1724,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120189875</v>
+        <v>120189870</v>
       </c>
       <c r="B12" t="n">
-        <v>57326</v>
+        <v>79160</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,21 +1740,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1759,10 +1764,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>781434</v>
+        <v>781383</v>
       </c>
       <c r="R12" t="n">
-        <v>7297219</v>
+        <v>7297243</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1821,10 +1826,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120189876</v>
+        <v>120189878</v>
       </c>
       <c r="B13" t="n">
-        <v>57421</v>
+        <v>78624</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1833,25 +1838,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>864</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1861,10 +1866,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>781433</v>
+        <v>781474</v>
       </c>
       <c r="R13" t="n">
-        <v>7297263</v>
+        <v>7297278</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1897,11 +1902,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>2st</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1928,10 +1928,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120189888</v>
+        <v>120189894</v>
       </c>
       <c r="B14" t="n">
-        <v>82305</v>
+        <v>95225</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1940,25 +1940,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>2869</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1968,10 +1968,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>781400</v>
+        <v>781369</v>
       </c>
       <c r="R14" t="n">
-        <v>7297236</v>
+        <v>7297222</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2030,10 +2030,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120189870</v>
+        <v>120189883</v>
       </c>
       <c r="B15" t="n">
-        <v>79144</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2046,21 +2046,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>781383</v>
+        <v>781413</v>
       </c>
       <c r="R15" t="n">
-        <v>7297243</v>
+        <v>7297244</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2132,10 +2132,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120189890</v>
+        <v>120189875</v>
       </c>
       <c r="B16" t="n">
-        <v>82305</v>
+        <v>57336</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2148,21 +2148,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>781400</v>
+        <v>781434</v>
       </c>
       <c r="R16" t="n">
-        <v>7297231</v>
+        <v>7297219</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2234,10 +2234,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120189877</v>
+        <v>120189892</v>
       </c>
       <c r="B17" t="n">
-        <v>93935</v>
+        <v>82321</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2246,25 +2246,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2387</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2274,10 +2274,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>781409</v>
+        <v>781383</v>
       </c>
       <c r="R17" t="n">
-        <v>7297244</v>
+        <v>7297238</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,10 +2336,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120189892</v>
+        <v>120189873</v>
       </c>
       <c r="B18" t="n">
-        <v>82305</v>
+        <v>90084</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2348,25 +2348,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>256703</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>781383</v>
+        <v>781452</v>
       </c>
       <c r="R18" t="n">
-        <v>7297238</v>
+        <v>7297230</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120189885</v>
+        <v>120189877</v>
       </c>
       <c r="B19" t="n">
-        <v>82305</v>
+        <v>93958</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2450,25 +2450,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>2387</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2478,10 +2478,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>781548</v>
+        <v>781409</v>
       </c>
       <c r="R19" t="n">
-        <v>7297260</v>
+        <v>7297244</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2540,10 +2540,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120189878</v>
+        <v>120189869</v>
       </c>
       <c r="B20" t="n">
-        <v>78608</v>
+        <v>90545</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2552,25 +2552,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>864</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>781474</v>
+        <v>781495</v>
       </c>
       <c r="R20" t="n">
-        <v>7297278</v>
+        <v>7297296</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2642,10 +2642,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120189894</v>
+        <v>120189888</v>
       </c>
       <c r="B21" t="n">
-        <v>95202</v>
+        <v>82321</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2654,25 +2654,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2869</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>781369</v>
+        <v>781400</v>
       </c>
       <c r="R21" t="n">
-        <v>7297222</v>
+        <v>7297236</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2747,7 +2747,7 @@
         <v>120275854</v>
       </c>
       <c r="B22" t="n">
-        <v>78608</v>
+        <v>78624</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2846,10 +2846,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120275859</v>
+        <v>120275860</v>
       </c>
       <c r="B23" t="n">
-        <v>74630</v>
+        <v>77926</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2862,16 +2862,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>308</v>
+        <v>6437</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2880,19 +2880,16 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lillträsk, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>781452</v>
+        <v>781459</v>
       </c>
       <c r="R23" t="n">
-        <v>7297246</v>
+        <v>7297274</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2933,7 +2930,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2952,10 +2948,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120275858</v>
+        <v>120275855</v>
       </c>
       <c r="B24" t="n">
-        <v>82305</v>
+        <v>78624</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2968,37 +2964,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lillträsk, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>781524</v>
+        <v>781492</v>
       </c>
       <c r="R24" t="n">
-        <v>7297322</v>
+        <v>7297238</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3039,7 +3032,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3051,17 +3043,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120275853</v>
+        <v>120275858</v>
       </c>
       <c r="B25" t="n">
-        <v>90724</v>
+        <v>82321</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3074,34 +3066,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1588</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lillträsk, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>781466</v>
+        <v>781524</v>
       </c>
       <c r="R25" t="n">
-        <v>7297264</v>
+        <v>7297322</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3142,6 +3137,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3153,17 +3149,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120275855</v>
+        <v>120275857</v>
       </c>
       <c r="B26" t="n">
-        <v>78608</v>
+        <v>56524</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3176,34 +3172,38 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>864</v>
+        <v>102612</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lillträsk, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>781492</v>
+        <v>781512</v>
       </c>
       <c r="R26" t="n">
-        <v>7297238</v>
+        <v>7297310</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3255,17 +3255,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120275857</v>
+        <v>120275859</v>
       </c>
       <c r="B27" t="n">
-        <v>56514</v>
+        <v>74646</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3278,27 +3278,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102612</v>
+        <v>308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3306,10 +3305,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>781512</v>
+        <v>781452</v>
       </c>
       <c r="R27" t="n">
-        <v>7297310</v>
+        <v>7297246</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3350,6 +3349,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3361,17 +3361,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120275860</v>
+        <v>120275853</v>
       </c>
       <c r="B28" t="n">
-        <v>77910</v>
+        <v>90742</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3384,21 +3384,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6437</v>
+        <v>1588</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3408,10 +3408,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>781459</v>
+        <v>781466</v>
       </c>
       <c r="R28" t="n">
-        <v>7297274</v>
+        <v>7297264</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 18646-2024 artfynd.xlsx
+++ b/artfynd/A 18646-2024 artfynd.xlsx
@@ -2744,10 +2744,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120275854</v>
+        <v>120275860</v>
       </c>
       <c r="B22" t="n">
-        <v>78624</v>
+        <v>77926</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2760,21 +2760,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>864</v>
+        <v>6437</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2784,10 +2784,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>781526</v>
+        <v>781459</v>
       </c>
       <c r="R22" t="n">
-        <v>7297306</v>
+        <v>7297274</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2846,10 +2846,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120275860</v>
+        <v>120275854</v>
       </c>
       <c r="B23" t="n">
-        <v>77926</v>
+        <v>78624</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2862,21 +2862,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6437</v>
+        <v>864</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>781459</v>
+        <v>781526</v>
       </c>
       <c r="R23" t="n">
-        <v>7297274</v>
+        <v>7297306</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 18646-2024 artfynd.xlsx
+++ b/artfynd/A 18646-2024 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120189882</v>
+        <v>120189893</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>781496</v>
+        <v>781372</v>
       </c>
       <c r="R3" t="n">
-        <v>7297260</v>
+        <v>7297233</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120189881</v>
+        <v>120189875</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>57336</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +919,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>781473</v>
+        <v>781434</v>
       </c>
       <c r="R4" t="n">
-        <v>7297275</v>
+        <v>7297219</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120189885</v>
+        <v>120189894</v>
       </c>
       <c r="B5" t="n">
-        <v>82321</v>
+        <v>95225</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,25 +1017,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781548</v>
+        <v>781369</v>
       </c>
       <c r="R5" t="n">
-        <v>7297260</v>
+        <v>7297222</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120189887</v>
+        <v>120189878</v>
       </c>
       <c r="B6" t="n">
-        <v>82321</v>
+        <v>78624</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,21 +1123,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1147,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>781443</v>
+        <v>781474</v>
       </c>
       <c r="R6" t="n">
-        <v>7297265</v>
+        <v>7297278</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120189879</v>
+        <v>120189885</v>
       </c>
       <c r="B7" t="n">
-        <v>78624</v>
+        <v>82321</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,21 +1225,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>781437</v>
+        <v>781548</v>
       </c>
       <c r="R7" t="n">
-        <v>7297264</v>
+        <v>7297260</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120189890</v>
+        <v>120189892</v>
       </c>
       <c r="B8" t="n">
         <v>82321</v>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>781400</v>
+        <v>781383</v>
       </c>
       <c r="R8" t="n">
-        <v>7297231</v>
+        <v>7297238</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,10 +1413,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120189893</v>
+        <v>120189876</v>
       </c>
       <c r="B9" t="n">
-        <v>82321</v>
+        <v>57431</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,25 +1425,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>103031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>781372</v>
+        <v>781433</v>
       </c>
       <c r="R9" t="n">
-        <v>7297233</v>
+        <v>7297263</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,6 +1489,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1515,10 +1520,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120189872</v>
+        <v>120189870</v>
       </c>
       <c r="B10" t="n">
-        <v>90600</v>
+        <v>79160</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,21 +1536,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1555,10 +1560,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>781492</v>
+        <v>781383</v>
       </c>
       <c r="R10" t="n">
-        <v>7297280</v>
+        <v>7297243</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,10 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120189876</v>
+        <v>120189879</v>
       </c>
       <c r="B11" t="n">
-        <v>57431</v>
+        <v>78624</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,25 +1634,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103031</v>
+        <v>864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1657,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>781433</v>
+        <v>781437</v>
       </c>
       <c r="R11" t="n">
-        <v>7297263</v>
+        <v>7297264</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,11 +1698,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2st</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1724,10 +1724,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120189870</v>
+        <v>120189882</v>
       </c>
       <c r="B12" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1740,21 +1740,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>781383</v>
+        <v>781496</v>
       </c>
       <c r="R12" t="n">
-        <v>7297243</v>
+        <v>7297260</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1826,10 +1826,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120189878</v>
+        <v>120189883</v>
       </c>
       <c r="B13" t="n">
-        <v>78624</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1842,21 +1842,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>781474</v>
+        <v>781413</v>
       </c>
       <c r="R13" t="n">
-        <v>7297278</v>
+        <v>7297244</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1928,10 +1928,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120189894</v>
+        <v>120189881</v>
       </c>
       <c r="B14" t="n">
-        <v>95225</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1940,25 +1940,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1968,10 +1968,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>781369</v>
+        <v>781473</v>
       </c>
       <c r="R14" t="n">
-        <v>7297222</v>
+        <v>7297275</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2030,10 +2030,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120189883</v>
+        <v>120189890</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2046,21 +2046,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>781413</v>
+        <v>781400</v>
       </c>
       <c r="R15" t="n">
-        <v>7297244</v>
+        <v>7297231</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2132,10 +2132,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120189875</v>
+        <v>120189877</v>
       </c>
       <c r="B16" t="n">
-        <v>57336</v>
+        <v>93958</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2144,25 +2144,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>2387</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>781434</v>
+        <v>781409</v>
       </c>
       <c r="R16" t="n">
-        <v>7297219</v>
+        <v>7297244</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2234,7 +2234,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120189892</v>
+        <v>120189887</v>
       </c>
       <c r="B17" t="n">
         <v>82321</v>
@@ -2274,10 +2274,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>781383</v>
+        <v>781443</v>
       </c>
       <c r="R17" t="n">
-        <v>7297238</v>
+        <v>7297265</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,10 +2336,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120189873</v>
+        <v>120189869</v>
       </c>
       <c r="B18" t="n">
-        <v>90084</v>
+        <v>90545</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2352,21 +2352,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>256703</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>781452</v>
+        <v>781495</v>
       </c>
       <c r="R18" t="n">
-        <v>7297230</v>
+        <v>7297296</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120189877</v>
+        <v>120189873</v>
       </c>
       <c r="B19" t="n">
-        <v>93958</v>
+        <v>90084</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2454,21 +2454,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2387</v>
+        <v>256703</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2478,10 +2478,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>781409</v>
+        <v>781452</v>
       </c>
       <c r="R19" t="n">
-        <v>7297244</v>
+        <v>7297230</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2540,10 +2540,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120189869</v>
+        <v>120189872</v>
       </c>
       <c r="B20" t="n">
-        <v>90545</v>
+        <v>90600</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2552,25 +2552,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>781495</v>
+        <v>781492</v>
       </c>
       <c r="R20" t="n">
-        <v>7297296</v>
+        <v>7297280</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2744,10 +2744,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120275860</v>
+        <v>120275859</v>
       </c>
       <c r="B22" t="n">
-        <v>77926</v>
+        <v>74646</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2760,16 +2760,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6437</v>
+        <v>308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2778,16 +2778,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lillträsk, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>781459</v>
+        <v>781452</v>
       </c>
       <c r="R22" t="n">
-        <v>7297274</v>
+        <v>7297246</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2828,6 +2831,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2846,10 +2850,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120275854</v>
+        <v>120275853</v>
       </c>
       <c r="B23" t="n">
-        <v>78624</v>
+        <v>90742</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2862,21 +2866,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>864</v>
+        <v>1588</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2886,10 +2890,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>781526</v>
+        <v>781466</v>
       </c>
       <c r="R23" t="n">
-        <v>7297306</v>
+        <v>7297264</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2948,7 +2952,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120275855</v>
+        <v>120275854</v>
       </c>
       <c r="B24" t="n">
         <v>78624</v>
@@ -2988,10 +2992,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>781492</v>
+        <v>781526</v>
       </c>
       <c r="R24" t="n">
-        <v>7297238</v>
+        <v>7297306</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3156,10 +3160,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120275857</v>
+        <v>120275855</v>
       </c>
       <c r="B26" t="n">
-        <v>56524</v>
+        <v>78624</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3172,38 +3176,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102612</v>
+        <v>864</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lillträsk, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>781512</v>
+        <v>781492</v>
       </c>
       <c r="R26" t="n">
-        <v>7297310</v>
+        <v>7297238</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3255,17 +3255,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120275859</v>
+        <v>120275860</v>
       </c>
       <c r="B27" t="n">
-        <v>74646</v>
+        <v>77926</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3278,16 +3278,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>308</v>
+        <v>6437</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3296,19 +3296,16 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lillträsk, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>781452</v>
+        <v>781459</v>
       </c>
       <c r="R27" t="n">
-        <v>7297246</v>
+        <v>7297274</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3349,7 +3346,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3368,10 +3364,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120275853</v>
+        <v>120275857</v>
       </c>
       <c r="B28" t="n">
-        <v>90742</v>
+        <v>56524</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3384,34 +3380,38 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1588</v>
+        <v>102612</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lillträsk, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>781466</v>
+        <v>781512</v>
       </c>
       <c r="R28" t="n">
-        <v>7297264</v>
+        <v>7297310</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>

--- a/artfynd/A 18646-2024 artfynd.xlsx
+++ b/artfynd/A 18646-2024 artfynd.xlsx
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120189894</v>
+        <v>120189878</v>
       </c>
       <c r="B5" t="n">
-        <v>95225</v>
+        <v>78624</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,25 +1017,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781369</v>
+        <v>781474</v>
       </c>
       <c r="R5" t="n">
-        <v>7297222</v>
+        <v>7297278</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120189878</v>
+        <v>120189894</v>
       </c>
       <c r="B6" t="n">
-        <v>78624</v>
+        <v>95225</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,25 +1119,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>864</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1147,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>781474</v>
+        <v>781369</v>
       </c>
       <c r="R6" t="n">
-        <v>7297278</v>
+        <v>7297222</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1520,10 +1520,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120189870</v>
+        <v>120189879</v>
       </c>
       <c r="B10" t="n">
-        <v>79160</v>
+        <v>78624</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,21 +1536,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1560,10 +1560,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>781383</v>
+        <v>781437</v>
       </c>
       <c r="R10" t="n">
-        <v>7297243</v>
+        <v>7297264</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,10 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120189879</v>
+        <v>120189870</v>
       </c>
       <c r="B11" t="n">
-        <v>78624</v>
+        <v>79160</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1638,21 +1638,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1662,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>781437</v>
+        <v>781383</v>
       </c>
       <c r="R11" t="n">
-        <v>7297264</v>
+        <v>7297243</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 18646-2024 artfynd.xlsx
+++ b/artfynd/A 18646-2024 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120189893</v>
+        <v>120189894</v>
       </c>
       <c r="B3" t="n">
-        <v>82321</v>
+        <v>95225</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,25 +813,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>2869</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>781372</v>
+        <v>781369</v>
       </c>
       <c r="R3" t="n">
-        <v>7297233</v>
+        <v>7297222</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120189875</v>
+        <v>120189893</v>
       </c>
       <c r="B4" t="n">
-        <v>57336</v>
+        <v>82321</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +919,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>781434</v>
+        <v>781372</v>
       </c>
       <c r="R4" t="n">
-        <v>7297219</v>
+        <v>7297233</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120189878</v>
+        <v>120189887</v>
       </c>
       <c r="B5" t="n">
-        <v>78624</v>
+        <v>82321</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,21 +1021,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781474</v>
+        <v>781443</v>
       </c>
       <c r="R5" t="n">
-        <v>7297278</v>
+        <v>7297265</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120189894</v>
+        <v>120189879</v>
       </c>
       <c r="B6" t="n">
-        <v>95225</v>
+        <v>78624</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,25 +1119,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1147,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>781369</v>
+        <v>781437</v>
       </c>
       <c r="R6" t="n">
-        <v>7297222</v>
+        <v>7297264</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120189885</v>
+        <v>120189872</v>
       </c>
       <c r="B7" t="n">
-        <v>82321</v>
+        <v>90600</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,21 +1225,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>781548</v>
+        <v>781492</v>
       </c>
       <c r="R7" t="n">
-        <v>7297260</v>
+        <v>7297280</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120189892</v>
+        <v>120189882</v>
       </c>
       <c r="B8" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>781383</v>
+        <v>781496</v>
       </c>
       <c r="R8" t="n">
-        <v>7297238</v>
+        <v>7297260</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,10 +1413,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120189876</v>
+        <v>120189885</v>
       </c>
       <c r="B9" t="n">
-        <v>57431</v>
+        <v>82321</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,25 +1425,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>781433</v>
+        <v>781548</v>
       </c>
       <c r="R9" t="n">
-        <v>7297263</v>
+        <v>7297260</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,11 +1489,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2st</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1520,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120189879</v>
+        <v>120189870</v>
       </c>
       <c r="B10" t="n">
-        <v>78624</v>
+        <v>79160</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,21 +1531,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1560,10 +1555,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>781437</v>
+        <v>781383</v>
       </c>
       <c r="R10" t="n">
-        <v>7297264</v>
+        <v>7297243</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,10 +1617,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120189870</v>
+        <v>120189877</v>
       </c>
       <c r="B11" t="n">
-        <v>79160</v>
+        <v>93958</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,25 +1629,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>2387</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1662,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>781383</v>
+        <v>781409</v>
       </c>
       <c r="R11" t="n">
-        <v>7297243</v>
+        <v>7297244</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120189882</v>
+        <v>120189878</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>78624</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1740,21 +1735,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1764,10 +1759,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>781496</v>
+        <v>781474</v>
       </c>
       <c r="R12" t="n">
-        <v>7297260</v>
+        <v>7297278</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1826,10 +1821,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120189883</v>
+        <v>120189888</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1842,21 +1837,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1866,10 +1861,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>781413</v>
+        <v>781400</v>
       </c>
       <c r="R13" t="n">
-        <v>7297244</v>
+        <v>7297236</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1928,10 +1923,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120189881</v>
+        <v>120189892</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1944,21 +1939,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1968,10 +1963,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>781473</v>
+        <v>781383</v>
       </c>
       <c r="R14" t="n">
-        <v>7297275</v>
+        <v>7297238</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2030,10 +2025,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120189890</v>
+        <v>120189873</v>
       </c>
       <c r="B15" t="n">
-        <v>82321</v>
+        <v>90084</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2042,25 +2037,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>256703</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2070,10 +2065,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>781400</v>
+        <v>781452</v>
       </c>
       <c r="R15" t="n">
-        <v>7297231</v>
+        <v>7297230</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2132,10 +2127,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120189877</v>
+        <v>120189890</v>
       </c>
       <c r="B16" t="n">
-        <v>93958</v>
+        <v>82321</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2144,25 +2139,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2387</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2172,10 +2167,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>781409</v>
+        <v>781400</v>
       </c>
       <c r="R16" t="n">
-        <v>7297244</v>
+        <v>7297231</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2234,10 +2229,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120189887</v>
+        <v>120189876</v>
       </c>
       <c r="B17" t="n">
-        <v>82321</v>
+        <v>57431</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2246,25 +2241,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>103031</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2274,10 +2269,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>781443</v>
+        <v>781433</v>
       </c>
       <c r="R17" t="n">
-        <v>7297265</v>
+        <v>7297263</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2310,6 +2305,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2336,10 +2336,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120189869</v>
+        <v>120189875</v>
       </c>
       <c r="B18" t="n">
-        <v>90545</v>
+        <v>57336</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2348,25 +2348,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>781495</v>
+        <v>781434</v>
       </c>
       <c r="R18" t="n">
-        <v>7297296</v>
+        <v>7297219</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120189873</v>
+        <v>120189883</v>
       </c>
       <c r="B19" t="n">
-        <v>90084</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2450,25 +2450,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>256703</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2478,10 +2478,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>781452</v>
+        <v>781413</v>
       </c>
       <c r="R19" t="n">
-        <v>7297230</v>
+        <v>7297244</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2540,10 +2540,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120189872</v>
+        <v>120189881</v>
       </c>
       <c r="B20" t="n">
-        <v>90600</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2556,21 +2556,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>781492</v>
+        <v>781473</v>
       </c>
       <c r="R20" t="n">
-        <v>7297280</v>
+        <v>7297275</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2642,10 +2642,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120189888</v>
+        <v>120189869</v>
       </c>
       <c r="B21" t="n">
-        <v>82321</v>
+        <v>90545</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2654,25 +2654,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>781400</v>
+        <v>781495</v>
       </c>
       <c r="R21" t="n">
-        <v>7297236</v>
+        <v>7297296</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2744,10 +2744,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120275859</v>
+        <v>120275853</v>
       </c>
       <c r="B22" t="n">
-        <v>74646</v>
+        <v>90742</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2760,37 +2760,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>308</v>
+        <v>1588</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lillträsk, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>781452</v>
+        <v>781466</v>
       </c>
       <c r="R22" t="n">
-        <v>7297246</v>
+        <v>7297264</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2831,7 +2828,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2850,10 +2846,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120275853</v>
+        <v>120275860</v>
       </c>
       <c r="B23" t="n">
-        <v>90742</v>
+        <v>77926</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2866,21 +2862,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1588</v>
+        <v>6437</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2890,10 +2886,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>781466</v>
+        <v>781459</v>
       </c>
       <c r="R23" t="n">
-        <v>7297264</v>
+        <v>7297274</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3054,10 +3050,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120275858</v>
+        <v>120275855</v>
       </c>
       <c r="B25" t="n">
-        <v>82321</v>
+        <v>78624</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3070,37 +3066,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lillträsk, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>781524</v>
+        <v>781492</v>
       </c>
       <c r="R25" t="n">
-        <v>7297322</v>
+        <v>7297238</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3141,7 +3134,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3153,17 +3145,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120275855</v>
+        <v>120275859</v>
       </c>
       <c r="B26" t="n">
-        <v>78624</v>
+        <v>74646</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3176,34 +3168,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>864</v>
+        <v>308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lillträsk, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>781492</v>
+        <v>781452</v>
       </c>
       <c r="R26" t="n">
-        <v>7297238</v>
+        <v>7297246</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3244,6 +3239,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3262,10 +3258,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120275860</v>
+        <v>120275857</v>
       </c>
       <c r="B27" t="n">
-        <v>77926</v>
+        <v>56524</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3278,34 +3274,38 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6437</v>
+        <v>102612</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lillträsk, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>781459</v>
+        <v>781512</v>
       </c>
       <c r="R27" t="n">
-        <v>7297274</v>
+        <v>7297310</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3357,17 +3357,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120275857</v>
+        <v>120275858</v>
       </c>
       <c r="B28" t="n">
-        <v>56524</v>
+        <v>82321</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3380,27 +3380,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102612</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3408,10 +3407,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>781512</v>
+        <v>781524</v>
       </c>
       <c r="R28" t="n">
-        <v>7297310</v>
+        <v>7297322</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3452,6 +3451,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 18646-2024 artfynd.xlsx
+++ b/artfynd/A 18646-2024 artfynd.xlsx
@@ -1923,10 +1923,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120189892</v>
+        <v>120189873</v>
       </c>
       <c r="B14" t="n">
-        <v>82321</v>
+        <v>90084</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,25 +1935,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>256703</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1963,10 +1963,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>781383</v>
+        <v>781452</v>
       </c>
       <c r="R14" t="n">
-        <v>7297238</v>
+        <v>7297230</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2025,10 +2025,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120189873</v>
+        <v>120189892</v>
       </c>
       <c r="B15" t="n">
-        <v>90084</v>
+        <v>82321</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,25 +2037,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>256703</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2065,10 +2065,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>781452</v>
+        <v>781383</v>
       </c>
       <c r="R15" t="n">
-        <v>7297230</v>
+        <v>7297238</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120189883</v>
+        <v>120189869</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2450,25 +2450,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2478,10 +2478,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>781413</v>
+        <v>781495</v>
       </c>
       <c r="R19" t="n">
-        <v>7297244</v>
+        <v>7297296</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2540,7 +2540,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120189881</v>
+        <v>120189883</v>
       </c>
       <c r="B20" t="n">
         <v>78542</v>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>781473</v>
+        <v>781413</v>
       </c>
       <c r="R20" t="n">
-        <v>7297275</v>
+        <v>7297244</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2642,10 +2642,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120189869</v>
+        <v>120189881</v>
       </c>
       <c r="B21" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2654,25 +2654,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>781495</v>
+        <v>781473</v>
       </c>
       <c r="R21" t="n">
-        <v>7297296</v>
+        <v>7297275</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 18646-2024 artfynd.xlsx
+++ b/artfynd/A 18646-2024 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120189894</v>
+        <v>120189888</v>
       </c>
       <c r="B3" t="n">
-        <v>95225</v>
+        <v>82321</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,25 +813,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2869</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>781369</v>
+        <v>781400</v>
       </c>
       <c r="R3" t="n">
-        <v>7297222</v>
+        <v>7297236</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120189893</v>
+        <v>120189883</v>
       </c>
       <c r="B4" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +919,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>781372</v>
+        <v>781413</v>
       </c>
       <c r="R4" t="n">
-        <v>7297233</v>
+        <v>7297244</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120189887</v>
+        <v>120189881</v>
       </c>
       <c r="B5" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,21 +1021,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781443</v>
+        <v>781473</v>
       </c>
       <c r="R5" t="n">
-        <v>7297265</v>
+        <v>7297275</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,7 +1107,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120189879</v>
+        <v>120189878</v>
       </c>
       <c r="B6" t="n">
         <v>78624</v>
@@ -1147,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>781437</v>
+        <v>781474</v>
       </c>
       <c r="R6" t="n">
-        <v>7297264</v>
+        <v>7297278</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120189872</v>
+        <v>120189887</v>
       </c>
       <c r="B7" t="n">
-        <v>90600</v>
+        <v>82321</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,21 +1225,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>781492</v>
+        <v>781443</v>
       </c>
       <c r="R7" t="n">
-        <v>7297280</v>
+        <v>7297265</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1413,10 +1413,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120189885</v>
+        <v>120189877</v>
       </c>
       <c r="B9" t="n">
-        <v>82321</v>
+        <v>93958</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,25 +1425,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>2387</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>781548</v>
+        <v>781409</v>
       </c>
       <c r="R9" t="n">
-        <v>7297260</v>
+        <v>7297244</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120189870</v>
+        <v>120189892</v>
       </c>
       <c r="B10" t="n">
-        <v>79160</v>
+        <v>82321</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,21 +1531,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1558,7 +1558,7 @@
         <v>781383</v>
       </c>
       <c r="R10" t="n">
-        <v>7297243</v>
+        <v>7297238</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,10 +1617,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120189877</v>
+        <v>120189870</v>
       </c>
       <c r="B11" t="n">
-        <v>93958</v>
+        <v>79160</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,25 +1629,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2387</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>781409</v>
+        <v>781383</v>
       </c>
       <c r="R11" t="n">
-        <v>7297244</v>
+        <v>7297243</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1719,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120189878</v>
+        <v>120189894</v>
       </c>
       <c r="B12" t="n">
-        <v>78624</v>
+        <v>95225</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,25 +1731,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>864</v>
+        <v>2869</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>781474</v>
+        <v>781369</v>
       </c>
       <c r="R12" t="n">
-        <v>7297278</v>
+        <v>7297222</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1821,7 +1821,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120189888</v>
+        <v>120189893</v>
       </c>
       <c r="B13" t="n">
         <v>82321</v>
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>781400</v>
+        <v>781372</v>
       </c>
       <c r="R13" t="n">
-        <v>7297236</v>
+        <v>7297233</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1923,10 +1923,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120189873</v>
+        <v>120189876</v>
       </c>
       <c r="B14" t="n">
-        <v>90084</v>
+        <v>57431</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1939,21 +1939,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>256703</v>
+        <v>103031</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1963,10 +1963,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>781452</v>
+        <v>781433</v>
       </c>
       <c r="R14" t="n">
-        <v>7297230</v>
+        <v>7297263</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1999,6 +1999,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2025,10 +2030,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120189892</v>
+        <v>120189875</v>
       </c>
       <c r="B15" t="n">
-        <v>82321</v>
+        <v>57336</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2041,21 +2046,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2065,10 +2070,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>781383</v>
+        <v>781434</v>
       </c>
       <c r="R15" t="n">
-        <v>7297238</v>
+        <v>7297219</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2127,10 +2132,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120189890</v>
+        <v>120189873</v>
       </c>
       <c r="B16" t="n">
-        <v>82321</v>
+        <v>90084</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2139,25 +2144,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>256703</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2167,10 +2172,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>781400</v>
+        <v>781452</v>
       </c>
       <c r="R16" t="n">
-        <v>7297231</v>
+        <v>7297230</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2229,10 +2234,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120189876</v>
+        <v>120189872</v>
       </c>
       <c r="B17" t="n">
-        <v>57431</v>
+        <v>90600</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2241,25 +2246,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103031</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2269,10 +2274,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>781433</v>
+        <v>781492</v>
       </c>
       <c r="R17" t="n">
-        <v>7297263</v>
+        <v>7297280</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2305,11 +2310,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>2st</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2336,10 +2336,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120189875</v>
+        <v>120189879</v>
       </c>
       <c r="B18" t="n">
-        <v>57336</v>
+        <v>78624</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2352,21 +2352,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>781434</v>
+        <v>781437</v>
       </c>
       <c r="R18" t="n">
-        <v>7297219</v>
+        <v>7297264</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120189869</v>
+        <v>120189890</v>
       </c>
       <c r="B19" t="n">
-        <v>90545</v>
+        <v>82321</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2450,25 +2450,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2478,10 +2478,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>781495</v>
+        <v>781400</v>
       </c>
       <c r="R19" t="n">
-        <v>7297296</v>
+        <v>7297231</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2540,10 +2540,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120189883</v>
+        <v>120189869</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2552,25 +2552,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>781413</v>
+        <v>781495</v>
       </c>
       <c r="R20" t="n">
-        <v>7297244</v>
+        <v>7297296</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2642,10 +2642,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120189881</v>
+        <v>120189885</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2658,21 +2658,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>781473</v>
+        <v>781548</v>
       </c>
       <c r="R21" t="n">
-        <v>7297275</v>
+        <v>7297260</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2744,10 +2744,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120275853</v>
+        <v>120275860</v>
       </c>
       <c r="B22" t="n">
-        <v>90742</v>
+        <v>77926</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2760,21 +2760,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1588</v>
+        <v>6437</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2784,10 +2784,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>781466</v>
+        <v>781459</v>
       </c>
       <c r="R22" t="n">
-        <v>7297264</v>
+        <v>7297274</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2846,10 +2846,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120275860</v>
+        <v>120275858</v>
       </c>
       <c r="B23" t="n">
-        <v>77926</v>
+        <v>82321</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2862,34 +2862,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6437</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lillträsk, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>781459</v>
+        <v>781524</v>
       </c>
       <c r="R23" t="n">
-        <v>7297274</v>
+        <v>7297322</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2930,6 +2933,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2941,17 +2945,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120275854</v>
+        <v>120275859</v>
       </c>
       <c r="B24" t="n">
-        <v>78624</v>
+        <v>74646</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2964,34 +2968,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>864</v>
+        <v>308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lillträsk, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>781526</v>
+        <v>781452</v>
       </c>
       <c r="R24" t="n">
-        <v>7297306</v>
+        <v>7297246</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3032,6 +3039,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3152,10 +3160,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120275859</v>
+        <v>120275857</v>
       </c>
       <c r="B26" t="n">
-        <v>74646</v>
+        <v>56524</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3168,26 +3176,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>308</v>
+        <v>102612</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3195,10 +3204,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>781452</v>
+        <v>781512</v>
       </c>
       <c r="R26" t="n">
-        <v>7297246</v>
+        <v>7297310</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3239,7 +3248,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3251,17 +3259,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120275857</v>
+        <v>120275853</v>
       </c>
       <c r="B27" t="n">
-        <v>56524</v>
+        <v>90742</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3274,38 +3282,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102612</v>
+        <v>1588</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lillträsk, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>781512</v>
+        <v>781466</v>
       </c>
       <c r="R27" t="n">
-        <v>7297310</v>
+        <v>7297264</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3357,17 +3361,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120275858</v>
+        <v>120275854</v>
       </c>
       <c r="B28" t="n">
-        <v>82321</v>
+        <v>78624</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3380,37 +3384,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lillträsk, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>781524</v>
+        <v>781526</v>
       </c>
       <c r="R28" t="n">
-        <v>7297322</v>
+        <v>7297306</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3451,7 +3452,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>

--- a/artfynd/A 18646-2024 artfynd.xlsx
+++ b/artfynd/A 18646-2024 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120189888</v>
+        <v>120189876</v>
       </c>
       <c r="B3" t="n">
-        <v>82321</v>
+        <v>57431</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,25 +813,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>103031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>781400</v>
+        <v>781433</v>
       </c>
       <c r="R3" t="n">
-        <v>7297236</v>
+        <v>7297263</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,6 +877,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120189883</v>
+        <v>120189888</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +924,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>781413</v>
+        <v>781400</v>
       </c>
       <c r="R4" t="n">
-        <v>7297244</v>
+        <v>7297236</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120189881</v>
+        <v>120189869</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,25 +1022,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1045,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781473</v>
+        <v>781495</v>
       </c>
       <c r="R5" t="n">
-        <v>7297275</v>
+        <v>7297296</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1209,7 +1214,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120189887</v>
+        <v>120189885</v>
       </c>
       <c r="B7" t="n">
         <v>82321</v>
@@ -1249,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>781443</v>
+        <v>781548</v>
       </c>
       <c r="R7" t="n">
-        <v>7297265</v>
+        <v>7297260</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,7 +1316,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120189882</v>
+        <v>120189881</v>
       </c>
       <c r="B8" t="n">
         <v>78542</v>
@@ -1351,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>781496</v>
+        <v>781473</v>
       </c>
       <c r="R8" t="n">
-        <v>7297260</v>
+        <v>7297275</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,10 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120189877</v>
+        <v>120189887</v>
       </c>
       <c r="B9" t="n">
-        <v>93958</v>
+        <v>82321</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,25 +1430,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2387</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1453,10 +1458,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>781409</v>
+        <v>781443</v>
       </c>
       <c r="R9" t="n">
-        <v>7297244</v>
+        <v>7297265</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,10 +1520,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120189892</v>
+        <v>120189883</v>
       </c>
       <c r="B10" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,21 +1536,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1555,10 +1560,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>781383</v>
+        <v>781413</v>
       </c>
       <c r="R10" t="n">
-        <v>7297238</v>
+        <v>7297244</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,10 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120189870</v>
+        <v>120189882</v>
       </c>
       <c r="B11" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,21 +1638,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1657,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>781383</v>
+        <v>781496</v>
       </c>
       <c r="R11" t="n">
-        <v>7297243</v>
+        <v>7297260</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1719,10 +1724,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120189894</v>
+        <v>120189890</v>
       </c>
       <c r="B12" t="n">
-        <v>95225</v>
+        <v>82321</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,25 +1736,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2869</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1759,10 +1764,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>781369</v>
+        <v>781400</v>
       </c>
       <c r="R12" t="n">
-        <v>7297222</v>
+        <v>7297231</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1821,10 +1826,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120189893</v>
+        <v>120189873</v>
       </c>
       <c r="B13" t="n">
-        <v>82321</v>
+        <v>90084</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1833,25 +1838,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>256703</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1861,10 +1866,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>781372</v>
+        <v>781452</v>
       </c>
       <c r="R13" t="n">
-        <v>7297233</v>
+        <v>7297230</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1923,10 +1928,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120189876</v>
+        <v>120189870</v>
       </c>
       <c r="B14" t="n">
-        <v>57431</v>
+        <v>79160</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,25 +1940,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103031</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1963,10 +1968,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>781433</v>
+        <v>781383</v>
       </c>
       <c r="R14" t="n">
-        <v>7297263</v>
+        <v>7297243</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1999,11 +2004,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>2st</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2030,10 +2030,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120189875</v>
+        <v>120189892</v>
       </c>
       <c r="B15" t="n">
-        <v>57336</v>
+        <v>82321</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2046,21 +2046,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>781434</v>
+        <v>781383</v>
       </c>
       <c r="R15" t="n">
-        <v>7297219</v>
+        <v>7297238</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2132,10 +2132,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120189873</v>
+        <v>120189893</v>
       </c>
       <c r="B16" t="n">
-        <v>90084</v>
+        <v>82321</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2144,25 +2144,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>256703</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>781452</v>
+        <v>781372</v>
       </c>
       <c r="R16" t="n">
-        <v>7297230</v>
+        <v>7297233</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2234,10 +2234,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120189872</v>
+        <v>120189894</v>
       </c>
       <c r="B17" t="n">
-        <v>90600</v>
+        <v>95225</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2246,25 +2246,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>2869</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2274,10 +2274,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>781492</v>
+        <v>781369</v>
       </c>
       <c r="R17" t="n">
-        <v>7297280</v>
+        <v>7297222</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,10 +2336,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120189879</v>
+        <v>120189877</v>
       </c>
       <c r="B18" t="n">
-        <v>78624</v>
+        <v>93958</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2348,25 +2348,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>2387</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>781437</v>
+        <v>781409</v>
       </c>
       <c r="R18" t="n">
-        <v>7297264</v>
+        <v>7297244</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120189890</v>
+        <v>120189875</v>
       </c>
       <c r="B19" t="n">
-        <v>82321</v>
+        <v>57336</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2454,21 +2454,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2478,10 +2478,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>781400</v>
+        <v>781434</v>
       </c>
       <c r="R19" t="n">
-        <v>7297231</v>
+        <v>7297219</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2540,10 +2540,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120189869</v>
+        <v>120189872</v>
       </c>
       <c r="B20" t="n">
-        <v>90545</v>
+        <v>90600</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2552,25 +2552,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>781495</v>
+        <v>781492</v>
       </c>
       <c r="R20" t="n">
-        <v>7297296</v>
+        <v>7297280</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2642,10 +2642,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120189885</v>
+        <v>120189879</v>
       </c>
       <c r="B21" t="n">
-        <v>82321</v>
+        <v>78624</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2658,21 +2658,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>781548</v>
+        <v>781437</v>
       </c>
       <c r="R21" t="n">
-        <v>7297260</v>
+        <v>7297264</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2744,10 +2744,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120275860</v>
+        <v>120275854</v>
       </c>
       <c r="B22" t="n">
-        <v>77926</v>
+        <v>78624</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2760,21 +2760,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6437</v>
+        <v>864</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2784,10 +2784,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>781459</v>
+        <v>781526</v>
       </c>
       <c r="R22" t="n">
-        <v>7297274</v>
+        <v>7297306</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2846,10 +2846,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120275858</v>
+        <v>120275857</v>
       </c>
       <c r="B23" t="n">
-        <v>82321</v>
+        <v>56524</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2862,26 +2862,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>102612</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2889,10 +2890,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>781524</v>
+        <v>781512</v>
       </c>
       <c r="R23" t="n">
-        <v>7297322</v>
+        <v>7297310</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2933,7 +2934,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2952,10 +2952,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120275859</v>
+        <v>120275853</v>
       </c>
       <c r="B24" t="n">
-        <v>74646</v>
+        <v>90742</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2968,37 +2968,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>308</v>
+        <v>1588</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lillträsk, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>781452</v>
+        <v>781466</v>
       </c>
       <c r="R24" t="n">
-        <v>7297246</v>
+        <v>7297264</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3039,7 +3036,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3160,10 +3156,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120275857</v>
+        <v>120275858</v>
       </c>
       <c r="B26" t="n">
-        <v>56524</v>
+        <v>82321</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3176,27 +3172,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102612</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3204,10 +3199,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>781512</v>
+        <v>781524</v>
       </c>
       <c r="R26" t="n">
-        <v>7297310</v>
+        <v>7297322</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3248,6 +3243,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3266,10 +3262,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120275853</v>
+        <v>120275860</v>
       </c>
       <c r="B27" t="n">
-        <v>90742</v>
+        <v>77926</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3282,21 +3278,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1588</v>
+        <v>6437</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3306,10 +3302,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>781466</v>
+        <v>781459</v>
       </c>
       <c r="R27" t="n">
-        <v>7297264</v>
+        <v>7297274</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3368,10 +3364,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120275854</v>
+        <v>120275859</v>
       </c>
       <c r="B28" t="n">
-        <v>78624</v>
+        <v>74646</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3384,34 +3380,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>864</v>
+        <v>308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lillträsk, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>781526</v>
+        <v>781452</v>
       </c>
       <c r="R28" t="n">
-        <v>7297306</v>
+        <v>7297246</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3452,6 +3451,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 18646-2024 artfynd.xlsx
+++ b/artfynd/A 18646-2024 artfynd.xlsx
@@ -1928,10 +1928,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120189870</v>
+        <v>120189892</v>
       </c>
       <c r="B14" t="n">
-        <v>79160</v>
+        <v>82321</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1944,21 +1944,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1971,7 +1971,7 @@
         <v>781383</v>
       </c>
       <c r="R14" t="n">
-        <v>7297243</v>
+        <v>7297238</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2030,10 +2030,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120189892</v>
+        <v>120189870</v>
       </c>
       <c r="B15" t="n">
-        <v>82321</v>
+        <v>79160</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2046,21 +2046,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2073,7 +2073,7 @@
         <v>781383</v>
       </c>
       <c r="R15" t="n">
-        <v>7297238</v>
+        <v>7297243</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 18646-2024 artfynd.xlsx
+++ b/artfynd/A 18646-2024 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120189876</v>
+        <v>120189894</v>
       </c>
       <c r="B3" t="n">
-        <v>57431</v>
+        <v>95225</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>2869</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>781433</v>
+        <v>781369</v>
       </c>
       <c r="R3" t="n">
-        <v>7297263</v>
+        <v>7297222</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,11 +877,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2st</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120189888</v>
+        <v>120189890</v>
       </c>
       <c r="B4" t="n">
         <v>82321</v>
@@ -951,7 +946,7 @@
         <v>781400</v>
       </c>
       <c r="R4" t="n">
-        <v>7297236</v>
+        <v>7297231</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120189869</v>
+        <v>120189892</v>
       </c>
       <c r="B5" t="n">
-        <v>90545</v>
+        <v>82321</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,25 +1017,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1050,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781495</v>
+        <v>781383</v>
       </c>
       <c r="R5" t="n">
-        <v>7297296</v>
+        <v>7297238</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120189878</v>
+        <v>120189875</v>
       </c>
       <c r="B6" t="n">
-        <v>78624</v>
+        <v>57336</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1128,21 +1123,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>864</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1152,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>781474</v>
+        <v>781434</v>
       </c>
       <c r="R6" t="n">
-        <v>7297278</v>
+        <v>7297219</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120189885</v>
+        <v>120189869</v>
       </c>
       <c r="B7" t="n">
-        <v>82321</v>
+        <v>90545</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,25 +1221,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1254,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>781548</v>
+        <v>781495</v>
       </c>
       <c r="R7" t="n">
-        <v>7297260</v>
+        <v>7297296</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120189881</v>
+        <v>120189883</v>
       </c>
       <c r="B8" t="n">
         <v>78542</v>
@@ -1356,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>781473</v>
+        <v>781413</v>
       </c>
       <c r="R8" t="n">
-        <v>7297275</v>
+        <v>7297244</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,10 +1413,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120189887</v>
+        <v>120189881</v>
       </c>
       <c r="B9" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,21 +1429,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1458,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>781443</v>
+        <v>781473</v>
       </c>
       <c r="R9" t="n">
-        <v>7297265</v>
+        <v>7297275</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1520,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120189883</v>
+        <v>120189877</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>93958</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,25 +1527,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2387</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1560,7 +1555,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>781413</v>
+        <v>781409</v>
       </c>
       <c r="R10" t="n">
         <v>7297244</v>
@@ -1622,10 +1617,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120189882</v>
+        <v>120189872</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>90600</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1638,21 +1633,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1662,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>781496</v>
+        <v>781492</v>
       </c>
       <c r="R11" t="n">
-        <v>7297260</v>
+        <v>7297280</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120189890</v>
+        <v>120189879</v>
       </c>
       <c r="B12" t="n">
-        <v>82321</v>
+        <v>78624</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1740,21 +1735,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1764,10 +1759,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>781400</v>
+        <v>781437</v>
       </c>
       <c r="R12" t="n">
-        <v>7297231</v>
+        <v>7297264</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1826,10 +1821,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120189873</v>
+        <v>120189893</v>
       </c>
       <c r="B13" t="n">
-        <v>90084</v>
+        <v>82321</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1838,25 +1833,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>256703</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1866,10 +1861,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>781452</v>
+        <v>781372</v>
       </c>
       <c r="R13" t="n">
-        <v>7297230</v>
+        <v>7297233</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1928,7 +1923,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120189892</v>
+        <v>120189885</v>
       </c>
       <c r="B14" t="n">
         <v>82321</v>
@@ -1968,10 +1963,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>781383</v>
+        <v>781548</v>
       </c>
       <c r="R14" t="n">
-        <v>7297238</v>
+        <v>7297260</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2030,10 +2025,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120189870</v>
+        <v>120189876</v>
       </c>
       <c r="B15" t="n">
-        <v>79160</v>
+        <v>57431</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2042,25 +2037,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2070,10 +2065,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>781383</v>
+        <v>781433</v>
       </c>
       <c r="R15" t="n">
-        <v>7297243</v>
+        <v>7297263</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2106,6 +2101,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2132,7 +2132,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120189893</v>
+        <v>120189887</v>
       </c>
       <c r="B16" t="n">
         <v>82321</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>781372</v>
+        <v>781443</v>
       </c>
       <c r="R16" t="n">
-        <v>7297233</v>
+        <v>7297265</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2234,10 +2234,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120189894</v>
+        <v>120189888</v>
       </c>
       <c r="B17" t="n">
-        <v>95225</v>
+        <v>82321</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2246,25 +2246,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2869</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2274,10 +2274,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>781369</v>
+        <v>781400</v>
       </c>
       <c r="R17" t="n">
-        <v>7297222</v>
+        <v>7297236</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,10 +2336,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120189877</v>
+        <v>120189878</v>
       </c>
       <c r="B18" t="n">
-        <v>93958</v>
+        <v>78624</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2348,25 +2348,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2387</v>
+        <v>864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>781409</v>
+        <v>781474</v>
       </c>
       <c r="R18" t="n">
-        <v>7297244</v>
+        <v>7297278</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120189875</v>
+        <v>120189870</v>
       </c>
       <c r="B19" t="n">
-        <v>57336</v>
+        <v>79160</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2454,21 +2454,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2478,10 +2478,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>781434</v>
+        <v>781383</v>
       </c>
       <c r="R19" t="n">
-        <v>7297219</v>
+        <v>7297243</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2540,10 +2540,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120189872</v>
+        <v>120189873</v>
       </c>
       <c r="B20" t="n">
-        <v>90600</v>
+        <v>90084</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2552,25 +2552,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>256703</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>781492</v>
+        <v>781452</v>
       </c>
       <c r="R20" t="n">
-        <v>7297280</v>
+        <v>7297230</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2642,10 +2642,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120189879</v>
+        <v>120189882</v>
       </c>
       <c r="B21" t="n">
-        <v>78624</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2658,21 +2658,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>781437</v>
+        <v>781496</v>
       </c>
       <c r="R21" t="n">
-        <v>7297264</v>
+        <v>7297260</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2744,10 +2744,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120275854</v>
+        <v>120275853</v>
       </c>
       <c r="B22" t="n">
-        <v>78624</v>
+        <v>90742</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2760,21 +2760,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>864</v>
+        <v>1588</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2784,10 +2784,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>781526</v>
+        <v>781466</v>
       </c>
       <c r="R22" t="n">
-        <v>7297306</v>
+        <v>7297264</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2846,10 +2846,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120275857</v>
+        <v>120275859</v>
       </c>
       <c r="B23" t="n">
-        <v>56524</v>
+        <v>74646</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2862,27 +2862,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102612</v>
+        <v>308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2890,10 +2889,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>781512</v>
+        <v>781452</v>
       </c>
       <c r="R23" t="n">
-        <v>7297310</v>
+        <v>7297246</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2934,6 +2933,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2945,17 +2945,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120275853</v>
+        <v>120275858</v>
       </c>
       <c r="B24" t="n">
-        <v>90742</v>
+        <v>82321</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2968,34 +2968,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1588</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lillträsk, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>781466</v>
+        <v>781524</v>
       </c>
       <c r="R24" t="n">
-        <v>7297264</v>
+        <v>7297322</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3036,6 +3039,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3047,7 +3051,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3156,10 +3160,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120275858</v>
+        <v>120275857</v>
       </c>
       <c r="B26" t="n">
-        <v>82321</v>
+        <v>56524</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3172,26 +3176,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>102612</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3199,10 +3204,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>781524</v>
+        <v>781512</v>
       </c>
       <c r="R26" t="n">
-        <v>7297322</v>
+        <v>7297310</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3243,7 +3248,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3262,10 +3266,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120275860</v>
+        <v>120275854</v>
       </c>
       <c r="B27" t="n">
-        <v>77926</v>
+        <v>78624</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3278,21 +3282,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6437</v>
+        <v>864</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3302,10 +3306,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>781459</v>
+        <v>781526</v>
       </c>
       <c r="R27" t="n">
-        <v>7297274</v>
+        <v>7297306</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3364,10 +3368,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120275859</v>
+        <v>120275860</v>
       </c>
       <c r="B28" t="n">
-        <v>74646</v>
+        <v>77926</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3380,16 +3384,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>308</v>
+        <v>6437</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3398,19 +3402,16 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lillträsk, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>781452</v>
+        <v>781459</v>
       </c>
       <c r="R28" t="n">
-        <v>7297246</v>
+        <v>7297274</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3451,7 +3452,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 18646-2024 artfynd.xlsx
+++ b/artfynd/A 18646-2024 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120189894</v>
+        <v>120189893</v>
       </c>
       <c r="B3" t="n">
-        <v>95225</v>
+        <v>82321</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,25 +813,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2869</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>781369</v>
+        <v>781372</v>
       </c>
       <c r="R3" t="n">
-        <v>7297222</v>
+        <v>7297233</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1005,7 +1005,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120189892</v>
+        <v>120189885</v>
       </c>
       <c r="B5" t="n">
         <v>82321</v>
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781383</v>
+        <v>781548</v>
       </c>
       <c r="R5" t="n">
-        <v>7297238</v>
+        <v>7297260</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120189875</v>
+        <v>120189877</v>
       </c>
       <c r="B6" t="n">
-        <v>57336</v>
+        <v>93958</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,25 +1119,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2387</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1147,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>781434</v>
+        <v>781409</v>
       </c>
       <c r="R6" t="n">
-        <v>7297219</v>
+        <v>7297244</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120189869</v>
+        <v>120189894</v>
       </c>
       <c r="B7" t="n">
-        <v>90545</v>
+        <v>95225</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,21 +1225,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>2869</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>781495</v>
+        <v>781369</v>
       </c>
       <c r="R7" t="n">
-        <v>7297296</v>
+        <v>7297222</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120189883</v>
+        <v>120189870</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>781413</v>
+        <v>781383</v>
       </c>
       <c r="R8" t="n">
-        <v>7297244</v>
+        <v>7297243</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,10 +1413,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120189881</v>
+        <v>120189876</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>57431</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,25 +1425,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>781473</v>
+        <v>781433</v>
       </c>
       <c r="R9" t="n">
-        <v>7297275</v>
+        <v>7297263</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,6 +1489,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1515,10 +1520,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120189877</v>
+        <v>120189878</v>
       </c>
       <c r="B10" t="n">
-        <v>93958</v>
+        <v>78624</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,25 +1532,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2387</v>
+        <v>864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1555,10 +1560,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>781409</v>
+        <v>781474</v>
       </c>
       <c r="R10" t="n">
-        <v>7297244</v>
+        <v>7297278</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,10 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120189872</v>
+        <v>120189887</v>
       </c>
       <c r="B11" t="n">
-        <v>90600</v>
+        <v>82321</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,21 +1638,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1657,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>781492</v>
+        <v>781443</v>
       </c>
       <c r="R11" t="n">
-        <v>7297280</v>
+        <v>7297265</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1719,10 +1724,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120189879</v>
+        <v>120189888</v>
       </c>
       <c r="B12" t="n">
-        <v>78624</v>
+        <v>82321</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,21 +1740,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1759,10 +1764,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>781437</v>
+        <v>781400</v>
       </c>
       <c r="R12" t="n">
-        <v>7297264</v>
+        <v>7297236</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1821,10 +1826,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120189893</v>
+        <v>120189881</v>
       </c>
       <c r="B13" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1837,21 +1842,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1861,10 +1866,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>781372</v>
+        <v>781473</v>
       </c>
       <c r="R13" t="n">
-        <v>7297233</v>
+        <v>7297275</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1923,10 +1928,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120189885</v>
+        <v>120189872</v>
       </c>
       <c r="B14" t="n">
-        <v>82321</v>
+        <v>90600</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1939,21 +1944,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1963,10 +1968,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>781548</v>
+        <v>781492</v>
       </c>
       <c r="R14" t="n">
-        <v>7297260</v>
+        <v>7297280</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2025,10 +2030,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120189876</v>
+        <v>120189892</v>
       </c>
       <c r="B15" t="n">
-        <v>57431</v>
+        <v>82321</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,25 +2042,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2065,10 +2070,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>781433</v>
+        <v>781383</v>
       </c>
       <c r="R15" t="n">
-        <v>7297263</v>
+        <v>7297238</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2101,11 +2106,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>2st</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2132,10 +2132,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120189887</v>
+        <v>120189875</v>
       </c>
       <c r="B16" t="n">
-        <v>82321</v>
+        <v>57336</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2148,21 +2148,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>781443</v>
+        <v>781434</v>
       </c>
       <c r="R16" t="n">
-        <v>7297265</v>
+        <v>7297219</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2234,10 +2234,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120189888</v>
+        <v>120189873</v>
       </c>
       <c r="B17" t="n">
-        <v>82321</v>
+        <v>90084</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2246,25 +2246,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>256703</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2274,10 +2274,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>781400</v>
+        <v>781452</v>
       </c>
       <c r="R17" t="n">
-        <v>7297236</v>
+        <v>7297230</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,10 +2336,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120189878</v>
+        <v>120189883</v>
       </c>
       <c r="B18" t="n">
-        <v>78624</v>
+        <v>78542</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2352,21 +2352,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>781474</v>
+        <v>781413</v>
       </c>
       <c r="R18" t="n">
-        <v>7297278</v>
+        <v>7297244</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120189870</v>
+        <v>120189882</v>
       </c>
       <c r="B19" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2454,21 +2454,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2478,10 +2478,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>781383</v>
+        <v>781496</v>
       </c>
       <c r="R19" t="n">
-        <v>7297243</v>
+        <v>7297260</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2540,10 +2540,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120189873</v>
+        <v>120189879</v>
       </c>
       <c r="B20" t="n">
-        <v>90084</v>
+        <v>78624</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2552,25 +2552,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>256703</v>
+        <v>864</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>781452</v>
+        <v>781437</v>
       </c>
       <c r="R20" t="n">
-        <v>7297230</v>
+        <v>7297264</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2642,10 +2642,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120189882</v>
+        <v>120189869</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2654,25 +2654,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>781496</v>
+        <v>781495</v>
       </c>
       <c r="R21" t="n">
-        <v>7297260</v>
+        <v>7297296</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2744,10 +2744,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120275853</v>
+        <v>120275859</v>
       </c>
       <c r="B22" t="n">
-        <v>90742</v>
+        <v>74646</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2760,34 +2760,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1588</v>
+        <v>308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lillträsk, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>781466</v>
+        <v>781452</v>
       </c>
       <c r="R22" t="n">
-        <v>7297264</v>
+        <v>7297246</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2828,6 +2831,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2846,10 +2850,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120275859</v>
+        <v>120275853</v>
       </c>
       <c r="B23" t="n">
-        <v>74646</v>
+        <v>90742</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2862,37 +2866,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>308</v>
+        <v>1588</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lillträsk, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>781452</v>
+        <v>781466</v>
       </c>
       <c r="R23" t="n">
-        <v>7297246</v>
+        <v>7297264</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2933,7 +2934,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2952,10 +2952,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120275858</v>
+        <v>120275860</v>
       </c>
       <c r="B24" t="n">
-        <v>82321</v>
+        <v>77926</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2968,37 +2968,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>6437</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lillträsk, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>781524</v>
+        <v>781459</v>
       </c>
       <c r="R24" t="n">
-        <v>7297322</v>
+        <v>7297274</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3039,7 +3036,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3051,7 +3047,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3160,10 +3156,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120275857</v>
+        <v>120275854</v>
       </c>
       <c r="B26" t="n">
-        <v>56524</v>
+        <v>78624</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3176,38 +3172,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102612</v>
+        <v>864</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lillträsk, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>781512</v>
+        <v>781526</v>
       </c>
       <c r="R26" t="n">
-        <v>7297310</v>
+        <v>7297306</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3259,17 +3251,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120275854</v>
+        <v>120275857</v>
       </c>
       <c r="B27" t="n">
-        <v>78624</v>
+        <v>56524</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3282,34 +3274,38 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>864</v>
+        <v>102612</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lillträsk, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>781526</v>
+        <v>781512</v>
       </c>
       <c r="R27" t="n">
-        <v>7297306</v>
+        <v>7297310</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3361,17 +3357,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120275860</v>
+        <v>120275858</v>
       </c>
       <c r="B28" t="n">
-        <v>77926</v>
+        <v>82321</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3384,34 +3380,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6437</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lillträsk, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>781459</v>
+        <v>781524</v>
       </c>
       <c r="R28" t="n">
-        <v>7297274</v>
+        <v>7297322</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3452,6 +3451,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>

--- a/artfynd/A 18646-2024 artfynd.xlsx
+++ b/artfynd/A 18646-2024 artfynd.xlsx
@@ -1413,10 +1413,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120189876</v>
+        <v>120189878</v>
       </c>
       <c r="B9" t="n">
-        <v>57431</v>
+        <v>78624</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,25 +1425,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>864</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>781433</v>
+        <v>781474</v>
       </c>
       <c r="R9" t="n">
-        <v>7297263</v>
+        <v>7297278</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,11 +1489,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2st</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1520,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120189878</v>
+        <v>120189876</v>
       </c>
       <c r="B10" t="n">
-        <v>78624</v>
+        <v>57431</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,25 +1527,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>864</v>
+        <v>103031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1560,10 +1555,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>781474</v>
+        <v>781433</v>
       </c>
       <c r="R10" t="n">
-        <v>7297278</v>
+        <v>7297263</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,6 +1591,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2132,10 +2132,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120189875</v>
+        <v>120189883</v>
       </c>
       <c r="B16" t="n">
-        <v>57336</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2148,21 +2148,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>781434</v>
+        <v>781413</v>
       </c>
       <c r="R16" t="n">
-        <v>7297219</v>
+        <v>7297244</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2234,10 +2234,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120189873</v>
+        <v>120189882</v>
       </c>
       <c r="B17" t="n">
-        <v>90084</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2246,25 +2246,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>256703</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2274,10 +2274,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>781452</v>
+        <v>781496</v>
       </c>
       <c r="R17" t="n">
-        <v>7297230</v>
+        <v>7297260</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,10 +2336,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120189883</v>
+        <v>120189875</v>
       </c>
       <c r="B18" t="n">
-        <v>78542</v>
+        <v>57336</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2352,21 +2352,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>781413</v>
+        <v>781434</v>
       </c>
       <c r="R18" t="n">
-        <v>7297244</v>
+        <v>7297219</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120189882</v>
+        <v>120189873</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>90084</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2450,25 +2450,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>256703</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2478,10 +2478,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>781496</v>
+        <v>781452</v>
       </c>
       <c r="R19" t="n">
-        <v>7297260</v>
+        <v>7297230</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3258,10 +3258,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120275857</v>
+        <v>120275858</v>
       </c>
       <c r="B27" t="n">
-        <v>56524</v>
+        <v>82321</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3274,27 +3274,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102612</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3302,10 +3301,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>781512</v>
+        <v>781524</v>
       </c>
       <c r="R27" t="n">
-        <v>7297310</v>
+        <v>7297322</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3346,6 +3345,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3364,10 +3364,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120275858</v>
+        <v>120275857</v>
       </c>
       <c r="B28" t="n">
-        <v>82321</v>
+        <v>56524</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3380,26 +3380,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>102612</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3407,10 +3408,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>781524</v>
+        <v>781512</v>
       </c>
       <c r="R28" t="n">
-        <v>7297322</v>
+        <v>7297310</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3451,7 +3452,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 18646-2024 artfynd.xlsx
+++ b/artfynd/A 18646-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90566583</v>
+        <v>120275859</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,14 +709,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillträsket_1, Nb</t>
+          <t>Lillträsk, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>781473.1112819064</v>
+        <v>781452</v>
       </c>
       <c r="R2" t="n">
-        <v>7297239.858339693</v>
+        <v>7297246</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-05-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-05-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,40 +761,25 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>gammal</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mariana Jussila Wahlberg</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mariana Jussila Wahlberg</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120189872</v>
+        <v>120189878</v>
       </c>
       <c r="B3" t="n">
-        <v>90600</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>781492</v>
+        <v>781474</v>
       </c>
       <c r="R3" t="n">
-        <v>7297280</v>
+        <v>7297278</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,37 +873,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120189873</v>
+        <v>120189879</v>
       </c>
       <c r="B4" t="n">
-        <v>90084</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>256703</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>781452</v>
+        <v>781437</v>
       </c>
       <c r="R4" t="n">
-        <v>7297230</v>
+        <v>7297264</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,15 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120189875</v>
+        <v>120275854</v>
       </c>
       <c r="B5" t="n">
-        <v>57336</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,21 +981,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1045,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781434</v>
+        <v>781526</v>
       </c>
       <c r="R5" t="n">
-        <v>7297219</v>
+        <v>7297306</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,12 +1035,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,15 +1067,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120189870</v>
+        <v>120275855</v>
       </c>
       <c r="B6" t="n">
-        <v>79160</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1123,21 +1078,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1147,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>781383</v>
+        <v>781492</v>
       </c>
       <c r="R6" t="n">
-        <v>7297243</v>
+        <v>7297238</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,12 +1132,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,15 +1164,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120189887</v>
+        <v>120189885</v>
       </c>
       <c r="B7" t="n">
-        <v>82321</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1249,10 +1199,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>781443</v>
+        <v>781548</v>
       </c>
       <c r="R7" t="n">
-        <v>7297265</v>
+        <v>7297260</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,37 +1261,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120189877</v>
+        <v>120189887</v>
       </c>
       <c r="B8" t="n">
-        <v>93958</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2387</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1296,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>781409</v>
+        <v>781443</v>
       </c>
       <c r="R8" t="n">
-        <v>7297244</v>
+        <v>7297265</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,15 +1358,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120189879</v>
+        <v>120189888</v>
       </c>
       <c r="B9" t="n">
-        <v>78624</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1429,21 +1369,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1453,10 +1393,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>781437</v>
+        <v>781400</v>
       </c>
       <c r="R9" t="n">
-        <v>7297264</v>
+        <v>7297236</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,15 +1455,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120189888</v>
+        <v>120189890</v>
       </c>
       <c r="B10" t="n">
-        <v>82321</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1558,7 +1493,7 @@
         <v>781400</v>
       </c>
       <c r="R10" t="n">
-        <v>7297236</v>
+        <v>7297231</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,15 +1552,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120189878</v>
+        <v>120189892</v>
       </c>
       <c r="B11" t="n">
-        <v>78624</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1633,21 +1563,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1657,10 +1587,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>781474</v>
+        <v>781383</v>
       </c>
       <c r="R11" t="n">
-        <v>7297278</v>
+        <v>7297238</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1719,15 +1649,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120189883</v>
+        <v>120189893</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1735,21 +1660,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1759,10 +1684,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>781413</v>
+        <v>781372</v>
       </c>
       <c r="R12" t="n">
-        <v>7297244</v>
+        <v>7297233</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1821,15 +1746,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120189893</v>
+        <v>120275858</v>
       </c>
       <c r="B13" t="n">
-        <v>82321</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1855,16 +1775,19 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lillträsk, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>781372</v>
+        <v>781524</v>
       </c>
       <c r="R13" t="n">
-        <v>7297233</v>
+        <v>7297322</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1891,12 +1814,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1905,6 +1828,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1916,22 +1840,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120189890</v>
+        <v>120275853</v>
       </c>
       <c r="B14" t="n">
-        <v>82321</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92097</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,21 +1858,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>1588</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1963,10 +1882,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>781400</v>
+        <v>781466</v>
       </c>
       <c r="R14" t="n">
-        <v>7297231</v>
+        <v>7297264</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1993,12 +1912,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2025,15 +1944,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120189876</v>
+        <v>120189877</v>
       </c>
       <c r="B15" t="n">
-        <v>57431</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95962</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,21 +1955,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>2387</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2065,10 +1979,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>781433</v>
+        <v>781409</v>
       </c>
       <c r="R15" t="n">
-        <v>7297263</v>
+        <v>7297244</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2101,11 +2015,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>2st</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2132,37 +2041,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120189885</v>
+        <v>120189894</v>
       </c>
       <c r="B16" t="n">
-        <v>82321</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>2869</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2172,10 +2076,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>781548</v>
+        <v>781369</v>
       </c>
       <c r="R16" t="n">
-        <v>7297260</v>
+        <v>7297222</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2234,15 +2138,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120189882</v>
+        <v>90566583</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,34 +2149,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lillträsk, Nb</t>
+          <t>Lillträsket_1, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>781496</v>
+        <v>781473</v>
       </c>
       <c r="R17" t="n">
-        <v>7297260</v>
+        <v>7297240</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2304,12 +2206,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2020-05-18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2020-05-18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2318,55 +2220,61 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>gammal</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mariana Jussila Wahlberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mariana Jussila Wahlberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120189894</v>
+        <v>120189872</v>
       </c>
       <c r="B18" t="n">
-        <v>95225</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2869</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2376,10 +2284,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>781369</v>
+        <v>781492</v>
       </c>
       <c r="R18" t="n">
-        <v>7297222</v>
+        <v>7297280</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,37 +2346,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120189881</v>
+        <v>120189869</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2478,10 +2381,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>781473</v>
+        <v>781495</v>
       </c>
       <c r="R19" t="n">
-        <v>7297275</v>
+        <v>7297296</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2540,37 +2443,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120189892</v>
+        <v>120189881</v>
       </c>
       <c r="B20" t="n">
-        <v>82321</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2580,10 +2478,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>781383</v>
+        <v>781473</v>
       </c>
       <c r="R20" t="n">
-        <v>7297238</v>
+        <v>7297275</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2642,37 +2540,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120189869</v>
+        <v>120189882</v>
       </c>
       <c r="B21" t="n">
-        <v>90545</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2682,10 +2575,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>781495</v>
+        <v>781496</v>
       </c>
       <c r="R21" t="n">
-        <v>7297296</v>
+        <v>7297260</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2744,37 +2637,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120275853</v>
+        <v>120189883</v>
       </c>
       <c r="B22" t="n">
-        <v>90796</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1588</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2784,10 +2672,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>781466</v>
+        <v>781413</v>
       </c>
       <c r="R22" t="n">
-        <v>7297264</v>
+        <v>7297244</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2814,12 +2702,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2846,15 +2734,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120275855</v>
+        <v>120275860</v>
       </c>
       <c r="B23" t="n">
-        <v>78642</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2862,21 +2745,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>864</v>
+        <v>6437</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2886,10 +2769,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>781492</v>
+        <v>781459</v>
       </c>
       <c r="R23" t="n">
-        <v>7297238</v>
+        <v>7297274</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2948,15 +2831,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120275858</v>
+        <v>120189870</v>
       </c>
       <c r="B24" t="n">
-        <v>82344</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2964,37 +2842,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lillträsk, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>781524</v>
+        <v>781383</v>
       </c>
       <c r="R24" t="n">
-        <v>7297322</v>
+        <v>7297243</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,12 +2896,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3035,7 +2910,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3047,44 +2921,39 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120275854</v>
+        <v>120189875</v>
       </c>
       <c r="B25" t="n">
-        <v>78642</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>864</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3094,10 +2963,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>781526</v>
+        <v>781434</v>
       </c>
       <c r="R25" t="n">
-        <v>7297306</v>
+        <v>7297219</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3124,12 +2993,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3159,16 +3028,11 @@
         <v>120275857</v>
       </c>
       <c r="B26" t="n">
-        <v>56536</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3262,15 +3126,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120275859</v>
+        <v>120189876</v>
       </c>
       <c r="B27" t="n">
-        <v>74661</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3278,37 +3137,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>308</v>
+        <v>103031</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lillträsk, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>781452</v>
+        <v>781433</v>
       </c>
       <c r="R27" t="n">
-        <v>7297246</v>
+        <v>7297263</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3335,12 +3191,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3349,7 +3210,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3368,15 +3228,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120275860</v>
+        <v>120189873</v>
       </c>
       <c r="B28" t="n">
-        <v>77944</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91402</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3384,21 +3239,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6437</v>
+        <v>256703</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3408,10 +3263,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>781459</v>
+        <v>781452</v>
       </c>
       <c r="R28" t="n">
-        <v>7297274</v>
+        <v>7297230</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3438,12 +3293,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 18646-2024 artfynd.xlsx
+++ b/artfynd/A 18646-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120275859</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120189878</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120189879</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120275854</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120275855</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120189885</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120189887</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,6 +1492,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120189888</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1549,6 +1594,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120189890</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1646,6 +1696,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120189892</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1743,6 +1798,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120189893</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1844,6 +1904,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120275858</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1941,6 +2006,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120275853</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2038,6 +2108,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120189877</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2135,6 +2210,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120189894</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2246,6 +2326,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90566583</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2343,6 +2428,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120189872</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2440,6 +2530,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120189869</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2537,6 +2632,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120189881</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2634,6 +2734,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120189882</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2731,6 +2836,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120189883</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2828,6 +2938,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120275860</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2925,6 +3040,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120189870</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3022,6 +3142,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120189875</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3123,6 +3248,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120275857</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3225,6 +3355,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120189876</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3322,8 +3457,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120189873</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>